--- a/www/download/IND.compensation.empe.s.us.WIOD16.xlsx
+++ b/www/download/IND.compensation.empe.s.us.WIOD16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>200799.080129438</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>187877.810512451</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>208739.334745531</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>267846.185293633</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>325683.950314428</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>362665.544935247</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>390912.181910073</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>474412.656057536</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>505430.862505818</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>487797.830144797</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>615284.235602794</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>739406.376609815</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>766015.670376561</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>740637.890223183</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>706818.003549762</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95449.81144</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94562.3738</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101697.48336</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>124410.84656</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140247.36159</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>144839.86374</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>153227.64824</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175685.08025</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>198501.66836</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>190005.9326</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>184146.88878</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>200925.3168</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>193159.91552</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>205254.53475</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>210681.7667</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118702.36504</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>121500.6784</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133246.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162403.44288</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>183766.3226</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>190165.16376</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>201197.344</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>231470.8716</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>262333.65296</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>250538.57884</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>242906.6853</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>266743.5312</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>254710.9576</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>269315.03982</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>271740.818543357</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4865.61147279986</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5260.26475498563</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5890.3219682804</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7561.84799754381</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9098.79701347324</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10301.9688820546</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11581.9492913645</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14820.1355371551</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19051.9301776586</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19074.1285685179</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18853.381674901</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20729.0518320841</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20142.4117247399</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22433.193698305</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24725.2041202312</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>261521.620925861</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>225368.877482007</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>207862.748106387</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>220064.149642965</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>262729.814033818</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>351578.78311947</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>436350.595752985</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>557819.431458893</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>681889.6530067</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>701113.876565657</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>919830.978221856</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>1103987.217297</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>1054164.13047212</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1070145.18482647</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1069813.78448037</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>372929.605623793</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>374176.318219081</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>384356.407150279</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>452631.199095672</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>513433.137727278</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>583467.528109265</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>666576.552287597</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>739209.93494322</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>790251.203873445</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>715676.82625622</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>814331.414559818</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>887322.549342821</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>921952.006178532</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0.933</t>
+          <t>932713.862982814</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.893</t>
+          <t>893438.294546591</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>588648.261561042</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>648537.417706858</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>708806.495508411</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>787189.110805554</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.924</t>
+          <t>923516.897971014</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1059897.96776983</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1251019.71548612</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1588322.70451862</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2.158</t>
+          <t>2157847.77481442</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2.479</t>
+          <t>2478568.29858374</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>3.036</t>
+          <t>3036441.33262075</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3.897</t>
+          <t>3896981.0192003</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>4.577</t>
+          <t>4577126.62759297</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5.159</t>
+          <t>5158719.31637214</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>5.666</t>
+          <t>5665835.26711</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3965.12589487155</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4083.26485042669</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4654.34206235087</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6080.74941449745</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7151.31062921035</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7664.24291363173</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8299.32260718529</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9621.60230544449</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11094.9724453315</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10751.7799173601</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11952.3438223168</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12937.4205930857</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11649.4486067851</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10911.2762094501</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10240.3864255101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23812.2236284</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26004.406438</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32564.7625809</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39719.6607316</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47276.559564</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54288.8954405</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61795.8543792</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74826.3245142</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95393.7676302</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82815.1582609</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83397.42159</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92051.0318287</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85054.1169208</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85596.2943009</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82643.038955</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>1034917.8136</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>1018950.0924</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>1082483.1648</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>1296600.6704</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.429</t>
+          <t>1428522.1258</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>1425585.5757</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1.463</t>
+          <t>1463134.3572</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>1640584.435</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1825664.3284</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.737</t>
+          <t>1737450.7524</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.699</t>
+          <t>1699498.3491</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1.861</t>
+          <t>1861484.016</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>1784833.8816</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1.897</t>
+          <t>1896981.0102</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1969899.23686706</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82179.05565</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83804.676459</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91763.513695</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112710.688379</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>127482.324004</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>133787.381465</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>142893.543975</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166047.481204</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>187223.966415</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>176874.697695</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>169882.00545</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>180356.642222817</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>168849.616694</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176314.68854</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>181400.783658557</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>289329.7068</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>302565.026</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>341068.464</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>436895.4576</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>511640.948</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>552435.1404</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>604134.4512</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>716162.998</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.823</t>
+          <t>823320.0116</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>765986.5004</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>717833.4075</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>739132.512</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>640603.8496</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>646293.303</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>652043.068069816</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2563.13702872089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2763.80602467209</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3238.75030361735</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4367.96985159235</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5313.07922046363</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6123.64543493402</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7404.24941561593</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10063.4532593967</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12066.0912700792</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9973.74685887986</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9223.65161777288</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10382.2632721936</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10207.2110358754</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11435.5003444188</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12397.646807778</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58700.3216</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60157.452</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>65515.896</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80279.0016</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91966.5026</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96766.098</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102623.9548</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118272.7795</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135288.5964</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126843.112</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>122499.9828</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134784.576</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>128850.0224</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134362.5489</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134693.958</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>694092.327</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>703433.7948</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>773290.404</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.952</t>
+          <t>952155.13456</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.084</t>
+          <t>1083643.01423</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>1123623.96861</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.183</t>
+          <t>1182790.76944</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>1342996.66895</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>1485794.806</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.413</t>
+          <t>1412950.5324</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>1379009.0484</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>1487949.168</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.403</t>
+          <t>1403458.9888</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1470227.9496</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1495258.36790236</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>814364.84151</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>825251.15572</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>889592.63064</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.016</t>
+          <t>1016324.81265</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.206</t>
+          <t>1205611.9926</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1255216.7712</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.356</t>
+          <t>1356310.19199</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.563</t>
+          <t>1563151.9456</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1467267.55844</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1243975.93376</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1266537.75147</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1.332</t>
+          <t>1332411.9968</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.348</t>
+          <t>1347599.10674</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1366098.33294</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.471</t>
+          <t>1470612.29592</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40651.5387280451</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42009.158390094</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>51107.8975575055</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67263.2563442507</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79781.2201755953</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84935.0372807456</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91741.8447831907</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>107502.82585072</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>121998.840506612</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118382.472582558</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108880.262444566</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101977.329588734</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84900.1206376122</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78783.4538319716</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77266.6846429039</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20558.814252</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23551.25002164</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29317.30844112</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37929.65912526</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45786.59288105</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50417.86347126</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50843.43744933</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62020.34095014</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70373.71167938</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57608.41724057</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55695.7600276</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59686.3019454</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54166.57312664</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56538.68658984</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57740.25998016</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53326.5837553719</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52222.90846428</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64428.790986977</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78557.935304634</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87303.5822310153</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96534.6268827779</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123403.916032795</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145496.806798059</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171928.368796653</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182407.24772453</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>237382.862769301</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>281371.725631559</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>289934.562725639</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>290335.076160917</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>284097.13937937</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101917.222659708</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>102234.588629987</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>104510.025359112</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115724.172628345</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>127502.864829729</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149617.068269718</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170606.630167237</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>220152.667377834</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>244960.764328012</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>256552.916381948</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>321233.782375547</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>379220.147199053</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>373926.282300288</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>382331.873657504</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>403566.934130755</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38546.7989693078</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41765.0523258937</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47350.3526900227</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61661.7119600428</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>73709.5339091297</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82221.287599275</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91349.2953698279</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109248.036998324</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>120191.716906966</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103493.602167895</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90713.9390466425</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95244.9552013011</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87291.753113915</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90732.3837710149</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93918.4403530152</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>423007.13752</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>432476.82136</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>477828.79536</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>595426.57664</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>678689.50338</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>708248.46378</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>746772.4946</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>845889.45715</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>940088.73564</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>885439.82252</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>851552.52426</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>0.907</t>
+          <t>906846.7968</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>826210.68288</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>847336.96389</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>855572.287729183</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>2467901.05404877</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2.125</t>
+          <t>2124892.09688782</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.012</t>
+          <t>2012027.95893069</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2189765.2133933</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2.323</t>
+          <t>2323326.13621388</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2.325</t>
+          <t>2325025.67422874</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.284</t>
+          <t>2283967.95758722</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2230458.83236105</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.533</t>
+          <t>2532930.44617965</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.648</t>
+          <t>2647996.04275366</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2.839</t>
+          <t>2839127.01333372</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3.102</t>
+          <t>3101639.5901877</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>3.078</t>
+          <t>3078394.0533017</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2.533</t>
+          <t>2532564.95184708</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2.335</t>
+          <t>2335376.08391695</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>212118.666420918</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>205125.88877233</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>232751.241204588</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>266242.591065472</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>299826.277731002</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>362045.614367676</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>415315.144594727</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>464960.373702264</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>430496.105215812</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>386653.211644653</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>464398.117486416</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>514693.705441813</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>533112.197938188</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>575010.397123815</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>630270.27255921</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4507.09782753862</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4631.44073402065</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5483.71337637463</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7287.65448879269</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9092.17999306117</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10599.0910269806</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12903.9475467813</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16893.134966628</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21113.5463021387</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16706.8492317145</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15205.9775842268</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17115.9845111989</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16673.0053321972</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18189.5694129926</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19257.6554408496</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9654.43153718084</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10358.7558690422</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11739.1667788993</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14467.4741478192</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16890.1227632074</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18057.4721744957</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19786.9901805449</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23563.7103941223</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27228.7867830864</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26515.1982463941</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26185.3719234795</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28867.6971003835</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27726.8008429228</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30593.4022807124</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32684.9309206109</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3282.8634921583</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3362.80295462533</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3660.65738905393</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4532.32639060765</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5539.43960164663</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6841.8139681184</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8928.31868381733</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13601.7250856622</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16877.2449687495</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11912.5949263967</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9947.65390490821</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11109.9993304544</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11112.5609327101</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12243.4944816405</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13091.9024182605</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171742.8713083</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>188027.137155134</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>202280.884133982</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>195260.282411858</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>201879.523821809</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>225437.777326331</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>246430.087205737</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>263754.445363993</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>282464.249866712</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>235024.781289102</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264819.135153495</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>289266.548738037</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>292813.589123655</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>314645.170657391</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>319940.303599964</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1785.54433566473</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1838.860702122</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2001.81793467317</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2436.47395366833</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2728.20225805487</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3073.21030878091</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3225.04177361075</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3731.43713926947</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4671.46050985369</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3790.56083303838</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3822.0849264098</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4430.37902021936</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4213.1947512616</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4575.46742803734</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4980.91920075766</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>208523.0192</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>213470.738</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>236419.8576</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>290548.72</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>324147.901</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>329284.6557</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>344034.4</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>398553.7345</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>451851.822</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>434502.5168</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>411344.8245</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>442438.848</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>414484.1888</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>429522.1491</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>436138.579</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71154.2378036678</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80656.4653655913</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79865.145559256</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85250.4738502308</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94235.1602700566</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112026.182488383</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125289.986440234</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>156722.429475063</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>207016.948478951</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>165207.130321154</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179859.835564439</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>194505.452790124</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>184004.736538528</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>195056.466998693</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>204113.582620104</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57101.8660596002</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58575.3300254107</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64705.2311535452</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79341.5406414</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>89973.1302613357</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94223.31582802</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97739.4729861959</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>111048.697915458</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123016.626414371</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116640.377253932</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112474.288475428</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113611.638066717</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96751.2161769926</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101307.715193514</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101288.661961636</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14776.9214008654</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16739.9524215496</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18196.0280096259</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22193.7519110302</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27954.0870827977</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38824.5658489559</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47076.9438653062</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63209.5582493684</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82226.1345725627</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>63485.6725745478</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59732.6189855976</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60900.7731633253</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56247.3780048832</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60804.2311549813</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66863.9578439625</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>92578.4111864287</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>113136.154108597</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134550.188450465</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>169464.783615425</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>235805.054083951</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>289567.341927265</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>375750.442596114</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>512270.390450192</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>616519.353154551</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>487965.085549919</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>576231.516526235</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>697566.227672211</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>770919.341032159</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>814770.693943947</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>755385.270610665</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8292.79040011203</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8382.68524780722</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9734.74574836978</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12946.373342093</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15582.4039699243</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17824.937422011</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20479.2173805289</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27196.7966887557</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34292.6288332079</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33476.1571940205</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33026.7533831632</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36265.8478538414</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34522.5704274247</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36412.6291403868</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37910.1140506309</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10215.5029263275</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10594.2522405958</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11849.4582801006</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14791.1381425738</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17224.1995529681</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18189.2630060511</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19654.2368885291</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23588.8416384073</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27880.6481792873</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26208.3513782914</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25212.5890368519</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26339.0103594949</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23763.6610044249</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23979.2453048522</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24390.6403759545</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117269.535183817</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110962.28844604</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>121982.378873636</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>151980.112674193</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>172780.705363304</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175940.884786701</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186435.19751026</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>219351.341539</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>238148.153825205</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>203967.363620203</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222528.63388409</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>260874.542279512</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>259875.863865115</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>278349.6733697</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>275409.608291217</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76869.9673612266</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56617.4271590379</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55005.4093037703</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>70453.9352684165</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90151.4940138017</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112258.716071965</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>121919.295275989</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151035.944678674</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>172520.277448417</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145363.508301631</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171310.339762505</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182130.472843148</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>187248.073575527</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>194768.50673348</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>191058.954525972</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>170774.341247462</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>155394.949713671</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>159055.676782522</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164509.213127444</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>179193.528410636</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>192719.072075031</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>199054.924746032</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>204728.28348972</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>211248.566539354</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>196274.535101574</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>222132.44770931</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>242611.077307756</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>245906.89339446</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>252814.559450188</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>259777.36864169</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5.863</t>
+          <t>5863150.00112362</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>6.054</t>
+          <t>6053753.00712748</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>6149709.00391068</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>6.373</t>
+          <t>6372707.99557373</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>6.749</t>
+          <t>6748782.00020607</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>7.098</t>
+          <t>7097916.00512548</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>7.514</t>
+          <t>7513699.0060963</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>7.909</t>
+          <t>7908768.99987201</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>8089961.98729939</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>7.796</t>
+          <t>7795659.99561757</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>7.969</t>
+          <t>7969484.99978942</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>8.277</t>
+          <t>8277114.98791631</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>8.619</t>
+          <t>8618539.00241532</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>8.849</t>
+          <t>8848749.99499199</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>9.258</t>
+          <t>9258365.00016341</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>1577655.48872709</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1570397.31840218</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>1515050.17604674</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.682</t>
+          <t>1682181.16082903</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1.964</t>
+          <t>1963842.74565605</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2.304</t>
+          <t>2303560.02040457</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2690001.09120825</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>3.173</t>
+          <t>3173291.60349065</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>3.804</t>
+          <t>3804383.88642882</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>3.601</t>
+          <t>3600867.44926011</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>4.151</t>
+          <t>4150857.06519537</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>4790426.73723502</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>5.184</t>
+          <t>5183989.64825557</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>5.353</t>
+          <t>5353375.60454835</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>5.459</t>
+          <t>5459132.07974466</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>16.707</t>
+          <t>16707186.0164064</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>16.614</t>
+          <t>16613738.5067708</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>17.113</t>
+          <t>17112591.9583954</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>19.044</t>
+          <t>19044350.1314139</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>21.132</t>
+          <t>21131723.9038133</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>22.635</t>
+          <t>22634969.1273193</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>24.438</t>
+          <t>24438270.7506687</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>27.329</t>
+          <t>27328567.7543659</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30229509.1438691</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>29.119</t>
+          <t>29118596.9345214</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>31.253</t>
+          <t>31252637.9623551</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>34720423.9905335</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>35.746</t>
+          <t>35746329.5963763</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>36.663</t>
+          <t>36662916.8074205</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>37.697</t>
+          <t>37696666.8173697</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11053.0420753764</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11170.9246754236</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13222.969897812</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17055.7280606209</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20099.0058384702</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21770.3847498731</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23824.2163175168</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28528.2800988921</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33710.4164008488</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31156.3227547357</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28959.0378783993</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29897.7428783456</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27043.1761608207</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27375.2798803056</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27133.60860391</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>159013.807839256</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>161506.796123523</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>174343.978557172</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>204274.930223031</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218870.414806918</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222748.280044263</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228679.229974057</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>249970.071984687</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>296972.509600384</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>295420.895290237</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>317641.843833139</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>387459.450856882</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>368851.830352167</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>378146.058253246</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>389253.428599351</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72915.5501116402</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75586.0398794097</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>89641.5211579208</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102854.018838523</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113942.755610106</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126651.961675891</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139105.301433405</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>169560.483458525</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>196014.3627115</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179520.170709978</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>191247.804084582</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>219225.33161615</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>225328.677503809</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>236163.18151627</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>230440.226408123</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>compensation.empe.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
